--- a/2d/results/best_unet_nofilter_projection_max/best_unet.xlsx
+++ b/2d/results/best_unet_nofilter_projection_max/best_unet.xlsx
@@ -535,55 +535,55 @@
         <v>140</v>
       </c>
       <c r="C2" t="n">
-        <v>12.52458728058108</v>
+        <v>20.49904283311987</v>
       </c>
       <c r="D2" t="n">
-        <v>20.499035563807</v>
+        <v>12.52457605167334</v>
       </c>
       <c r="E2" t="n">
-        <v>39.13695226839486</v>
+        <v>39.1369232159589</v>
       </c>
       <c r="F2" t="n">
-        <v>13.21549548355105</v>
+        <v>13.21549753058586</v>
       </c>
       <c r="G2" t="n">
-        <v>10.62963021156498</v>
+        <v>10.62963219284083</v>
       </c>
       <c r="H2" t="n">
-        <v>77.87705423694847</v>
+        <v>77.87706031237225</v>
       </c>
       <c r="I2" t="n">
-        <v>74.0385085287884</v>
+        <v>74.03852880714756</v>
       </c>
       <c r="J2" t="n">
-        <v>65.49213060677351</v>
+        <v>65.49213725717293</v>
       </c>
       <c r="K2" t="n">
-        <v>63.97594680737009</v>
+        <v>63.97596420931025</v>
       </c>
       <c r="L2" t="n">
-        <v>38.2812126911769</v>
+        <v>38.2812065058835</v>
       </c>
       <c r="M2" t="n">
-        <v>31.38764923421753</v>
+        <v>31.387654515447</v>
       </c>
       <c r="N2" t="n">
-        <v>73.70862788033658</v>
+        <v>73.70863277078395</v>
       </c>
       <c r="O2" t="n">
-        <v>62.27465460975466</v>
+        <v>62.27466674803021</v>
       </c>
       <c r="P2" t="n">
-        <v>21.85434036482477</v>
+        <v>21.85434598001351</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.5155253580748</v>
+        <v>21.51553412451567</v>
       </c>
       <c r="R2" t="n">
-        <v>21.16815161728019</v>
+        <v>21.16816364248647</v>
       </c>
       <c r="S2" t="n">
-        <v>22.40760304973032</v>
+        <v>22.40760878049781</v>
       </c>
     </row>
     <row r="3">
@@ -596,55 +596,55 @@
         <v>141</v>
       </c>
       <c r="C3" t="n">
-        <v>8.794682948536177</v>
+        <v>13.99224099699725</v>
       </c>
       <c r="D3" t="n">
-        <v>13.99223287132112</v>
+        <v>8.794688210870428</v>
       </c>
       <c r="E3" t="n">
-        <v>30.12157555397705</v>
+        <v>30.12154322452308</v>
       </c>
       <c r="F3" t="n">
-        <v>21.57314829598851</v>
+        <v>21.57314533112797</v>
       </c>
       <c r="G3" t="n">
-        <v>16.2892516306584</v>
+        <v>16.28924917968719</v>
       </c>
       <c r="H3" t="n">
-        <v>81.92008463010961</v>
+        <v>81.9200745561927</v>
       </c>
       <c r="I3" t="n">
-        <v>88.85119704148916</v>
+        <v>88.85118004293436</v>
       </c>
       <c r="J3" t="n">
-        <v>71.96862029585525</v>
+        <v>71.96860652063891</v>
       </c>
       <c r="K3" t="n">
-        <v>78.61144259780424</v>
+        <v>78.61143581267639</v>
       </c>
       <c r="L3" t="n">
-        <v>55.34586418857187</v>
+        <v>55.34586166600285</v>
       </c>
       <c r="M3" t="n">
-        <v>44.86434950985216</v>
+        <v>44.86435553846503</v>
       </c>
       <c r="N3" t="n">
-        <v>80.97745356930699</v>
+        <v>80.97743688818984</v>
       </c>
       <c r="O3" t="n">
-        <v>71.71696994084537</v>
+        <v>71.71699148228927</v>
       </c>
       <c r="P3" t="n">
-        <v>14.86718165691219</v>
+        <v>14.86719082399782</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.31677884624408</v>
+        <v>14.31678480665137</v>
       </c>
       <c r="R3" t="n">
-        <v>15.40495788659813</v>
+        <v>15.40497692320785</v>
       </c>
       <c r="S3" t="n">
-        <v>14.34456641511817</v>
+        <v>14.34458512670731</v>
       </c>
     </row>
     <row r="4">
@@ -657,55 +657,55 @@
         <v>149</v>
       </c>
       <c r="C4" t="n">
-        <v>8.992934643606398</v>
+        <v>9.747684072554899</v>
       </c>
       <c r="D4" t="n">
-        <v>9.747678626585001</v>
+        <v>8.992947897165898</v>
       </c>
       <c r="E4" t="n">
-        <v>17.31702054453676</v>
+        <v>17.31701246194098</v>
       </c>
       <c r="F4" t="n">
-        <v>11.22912846741689</v>
+        <v>11.22912751715172</v>
       </c>
       <c r="G4" t="n">
-        <v>9.326821340350293</v>
+        <v>9.326822388156794</v>
       </c>
       <c r="H4" t="n">
-        <v>83.69717594256417</v>
+        <v>83.69719260942017</v>
       </c>
       <c r="I4" t="n">
-        <v>74.63558930857853</v>
+        <v>74.63556526714429</v>
       </c>
       <c r="J4" t="n">
-        <v>71.66144392105953</v>
+        <v>71.66145464944898</v>
       </c>
       <c r="K4" t="n">
-        <v>64.94638177527284</v>
+        <v>64.94637488154302</v>
       </c>
       <c r="L4" t="n">
-        <v>33.62715806182162</v>
+        <v>33.62717534537394</v>
       </c>
       <c r="M4" t="n">
-        <v>27.22987113327268</v>
+        <v>27.22986394378596</v>
       </c>
       <c r="N4" t="n">
-        <v>77.49978375049697</v>
+        <v>77.49978766405916</v>
       </c>
       <c r="O4" t="n">
-        <v>66.85768525733924</v>
+        <v>66.85769590960682</v>
       </c>
       <c r="P4" t="n">
-        <v>15.20899495590065</v>
+        <v>15.20904248013925</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.95762233073437</v>
+        <v>16.95763638770714</v>
       </c>
       <c r="R4" t="n">
-        <v>18.92711585570872</v>
+        <v>18.92709261040561</v>
       </c>
       <c r="S4" t="n">
-        <v>17.27671789066667</v>
+        <v>17.2767030058125</v>
       </c>
     </row>
     <row r="5">
@@ -718,55 +718,55 @@
         <v>160</v>
       </c>
       <c r="C5" t="n">
-        <v>12.55164035375562</v>
+        <v>18.2538172869583</v>
       </c>
       <c r="D5" t="n">
-        <v>18.25380922818924</v>
+        <v>12.55164052255571</v>
       </c>
       <c r="E5" t="n">
-        <v>41.62514073100509</v>
+        <v>41.62515501020552</v>
       </c>
       <c r="F5" t="n">
-        <v>11.35221477510676</v>
+        <v>11.3522140070596</v>
       </c>
       <c r="G5" t="n">
-        <v>8.307197131015567</v>
+        <v>8.307198746283692</v>
       </c>
       <c r="H5" t="n">
-        <v>69.1308580329796</v>
+        <v>69.13085646270271</v>
       </c>
       <c r="I5" t="n">
-        <v>67.954984042677</v>
+        <v>67.95497720904854</v>
       </c>
       <c r="J5" t="n">
-        <v>55.21007770021883</v>
+        <v>55.21008124573568</v>
       </c>
       <c r="K5" t="n">
-        <v>53.53136684335328</v>
+        <v>53.53137626865396</v>
       </c>
       <c r="L5" t="n">
-        <v>35.7969877108928</v>
+        <v>35.79698719995523</v>
       </c>
       <c r="M5" t="n">
-        <v>30.07591147483959</v>
+        <v>30.0759247699961</v>
       </c>
       <c r="N5" t="n">
-        <v>66.46437965675537</v>
+        <v>66.46433618190615</v>
       </c>
       <c r="O5" t="n">
-        <v>51.69720565816608</v>
+        <v>51.69721577053483</v>
       </c>
       <c r="P5" t="n">
-        <v>26.04479088558466</v>
+        <v>26.04479473885856</v>
       </c>
       <c r="Q5" t="n">
-        <v>25.09504147423742</v>
+        <v>25.09503587734168</v>
       </c>
       <c r="R5" t="n">
-        <v>24.89935659067681</v>
+        <v>24.89938413957432</v>
       </c>
       <c r="S5" t="n">
-        <v>26.13959759290954</v>
+        <v>26.13955123026939</v>
       </c>
     </row>
     <row r="6">
@@ -779,55 +779,55 @@
         <v>170</v>
       </c>
       <c r="C6" t="n">
-        <v>9.361367750206352</v>
+        <v>15.56077127328608</v>
       </c>
       <c r="D6" t="n">
-        <v>15.56077792968888</v>
+        <v>9.361367779630703</v>
       </c>
       <c r="E6" t="n">
-        <v>24.95310961831181</v>
+        <v>24.95314342826614</v>
       </c>
       <c r="F6" t="n">
-        <v>15.29998126941543</v>
+        <v>15.29998389802067</v>
       </c>
       <c r="G6" t="n">
-        <v>11.48216017167702</v>
+        <v>11.48215697144594</v>
       </c>
       <c r="H6" t="n">
-        <v>80.5163386156092</v>
+        <v>80.51633563309825</v>
       </c>
       <c r="I6" t="n">
-        <v>75.5996641911146</v>
+        <v>75.59966507624627</v>
       </c>
       <c r="J6" t="n">
         <v>57.79641390005387</v>
       </c>
       <c r="K6" t="n">
-        <v>62.26920495353823</v>
+        <v>62.26919126831923</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75994289588252</v>
+        <v>42.75994258344779</v>
       </c>
       <c r="M6" t="n">
-        <v>37.99697018100198</v>
+        <v>37.9969693086047</v>
       </c>
       <c r="N6" t="n">
-        <v>74.95035777986323</v>
+        <v>74.95035297349176</v>
       </c>
       <c r="O6" t="n">
-        <v>56.62665196096469</v>
+        <v>56.62663987584099</v>
       </c>
       <c r="P6" t="n">
-        <v>29.2853352918546</v>
+        <v>29.28536532905791</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.24153801842009</v>
+        <v>24.2415670485119</v>
       </c>
       <c r="R6" t="n">
-        <v>18.92803167934637</v>
+        <v>18.92805975002668</v>
       </c>
       <c r="S6" t="n">
-        <v>26.56133677464386</v>
+        <v>26.56136801113639</v>
       </c>
     </row>
     <row r="7">
@@ -840,19 +840,19 @@
         <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>10.68152035781189</v>
+        <v>13.41706728782088</v>
       </c>
       <c r="D7" t="n">
-        <v>13.41706361970178</v>
+        <v>10.68150665678733</v>
       </c>
       <c r="E7" t="n">
-        <v>26.97618867621664</v>
+        <v>26.97616734959997</v>
       </c>
       <c r="F7" t="n">
-        <v>12.7126881800154</v>
+        <v>12.71268822455215</v>
       </c>
       <c r="G7" t="n">
-        <v>9.586008157328175</v>
+        <v>9.58601204667168</v>
       </c>
       <c r="H7" t="n">
         <v>80.60984066773732</v>
@@ -861,34 +861,34 @@
         <v>74.33394301207791</v>
       </c>
       <c r="J7" t="n">
-        <v>65.86129965526683</v>
+        <v>65.86130614331073</v>
       </c>
       <c r="K7" t="n">
-        <v>64.17770925434203</v>
+        <v>64.17769329334402</v>
       </c>
       <c r="L7" t="n">
-        <v>35.66327999255255</v>
+        <v>35.66327140190991</v>
       </c>
       <c r="M7" t="n">
-        <v>28.58038670764573</v>
+        <v>28.58039293499436</v>
       </c>
       <c r="N7" t="n">
-        <v>74.63399174155951</v>
+        <v>74.63399332718927</v>
       </c>
       <c r="O7" t="n">
-        <v>63.79413980399445</v>
+        <v>63.79415123125349</v>
       </c>
       <c r="P7" t="n">
-        <v>20.1036727148358</v>
+        <v>20.10368087334519</v>
       </c>
       <c r="Q7" t="n">
-        <v>19.35179231691811</v>
+        <v>19.35179946156579</v>
       </c>
       <c r="R7" t="n">
-        <v>18.52827217684981</v>
+        <v>18.52827823965129</v>
       </c>
       <c r="S7" t="n">
-        <v>18.86491032578355</v>
+        <v>18.86491407429363</v>
       </c>
     </row>
     <row r="8">
@@ -901,55 +901,55 @@
         <v>190</v>
       </c>
       <c r="C8" t="n">
-        <v>4.896866544920664</v>
+        <v>11.67889609397331</v>
       </c>
       <c r="D8" t="n">
-        <v>11.6789013903414</v>
+        <v>4.896858663447884</v>
       </c>
       <c r="E8" t="n">
-        <v>34.58465297331819</v>
+        <v>34.58458452998283</v>
       </c>
       <c r="F8" t="n">
-        <v>17.39674026161432</v>
+        <v>17.396728366405</v>
       </c>
       <c r="G8" t="n">
-        <v>11.41095026528412</v>
+        <v>11.41095454144132</v>
       </c>
       <c r="H8" t="n">
         <v>97.87542353418677</v>
       </c>
       <c r="I8" t="n">
-        <v>88.68201031825632</v>
+        <v>88.68199976975174</v>
       </c>
       <c r="J8" t="n">
-        <v>68.8493875506795</v>
+        <v>68.84939453821424</v>
       </c>
       <c r="K8" t="n">
-        <v>71.00939272578115</v>
+        <v>71.00940350618367</v>
       </c>
       <c r="L8" t="n">
-        <v>40.937807021339</v>
+        <v>40.93781122284466</v>
       </c>
       <c r="M8" t="n">
-        <v>33.07906006240307</v>
+        <v>33.07906915159433</v>
       </c>
       <c r="N8" t="n">
-        <v>91.31837823401047</v>
+        <v>91.31837283925955</v>
       </c>
       <c r="O8" t="n">
-        <v>68.41639116667849</v>
+        <v>68.41639334002926</v>
       </c>
       <c r="P8" t="n">
-        <v>29.65610255915654</v>
+        <v>29.65609541994376</v>
       </c>
       <c r="Q8" t="n">
-        <v>25.03178383817102</v>
+        <v>25.03177007513627</v>
       </c>
       <c r="R8" t="n">
-        <v>19.92807507300839</v>
+        <v>19.92805339240439</v>
       </c>
       <c r="S8" t="n">
-        <v>25.07927485160089</v>
+        <v>25.07926804559123</v>
       </c>
     </row>
     <row r="9">
@@ -962,55 +962,55 @@
         <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>14.91290646051224</v>
+        <v>23.45414375702097</v>
       </c>
       <c r="D9" t="n">
-        <v>23.45414939853007</v>
+        <v>14.91290377942081</v>
       </c>
       <c r="E9" t="n">
-        <v>21.18646528252455</v>
+        <v>21.18649475719666</v>
       </c>
       <c r="F9" t="n">
-        <v>14.65914917979921</v>
+        <v>14.65915202702977</v>
       </c>
       <c r="G9" t="n">
-        <v>11.80485407526926</v>
+        <v>11.80485360232924</v>
       </c>
       <c r="H9" t="n">
-        <v>83.98921300374411</v>
+        <v>83.98920640682978</v>
       </c>
       <c r="I9" t="n">
-        <v>77.03536761799204</v>
+        <v>77.03537330142511</v>
       </c>
       <c r="J9" t="n">
-        <v>70.90261036274011</v>
+        <v>70.90262682456903</v>
       </c>
       <c r="K9" t="n">
-        <v>65.94595189830494</v>
+        <v>65.94594096369964</v>
       </c>
       <c r="L9" t="n">
-        <v>40.73066421543524</v>
+        <v>40.73066951357511</v>
       </c>
       <c r="M9" t="n">
-        <v>35.53665449361355</v>
+        <v>35.53665065362953</v>
       </c>
       <c r="N9" t="n">
-        <v>78.6040993165377</v>
+        <v>78.60409901112003</v>
       </c>
       <c r="O9" t="n">
-        <v>66.27240244213384</v>
+        <v>66.27242374925174</v>
       </c>
       <c r="P9" t="n">
-        <v>17.55689475038815</v>
+        <v>17.556888274912</v>
       </c>
       <c r="Q9" t="n">
-        <v>17.14184649373897</v>
+        <v>17.14185925656118</v>
       </c>
       <c r="R9" t="n">
-        <v>16.68933257042778</v>
+        <v>16.68936637707971</v>
       </c>
       <c r="S9" t="n">
-        <v>18.30824557649228</v>
+        <v>18.30823360989051</v>
       </c>
     </row>
     <row r="10">
@@ -1023,55 +1023,55 @@
         <v>199</v>
       </c>
       <c r="C10" t="n">
-        <v>9.608493813245758</v>
+        <v>14.29815362977604</v>
       </c>
       <c r="D10" t="n">
-        <v>14.29814710927321</v>
+        <v>9.60849285555436</v>
       </c>
       <c r="E10" t="n">
-        <v>36.4204306083509</v>
+        <v>36.42042255407032</v>
       </c>
       <c r="F10" t="n">
-        <v>13.3867092264093</v>
+        <v>13.38671015281071</v>
       </c>
       <c r="G10" t="n">
-        <v>8.511212081863192</v>
+        <v>8.511213749068414</v>
       </c>
       <c r="H10" t="n">
-        <v>79.69721017887015</v>
+        <v>79.69720583881453</v>
       </c>
       <c r="I10" t="n">
-        <v>76.92826610366369</v>
+        <v>76.92824594941679</v>
       </c>
       <c r="J10" t="n">
         <v>64.51700062321238</v>
       </c>
       <c r="K10" t="n">
-        <v>66.92565421971081</v>
+        <v>66.92563629670538</v>
       </c>
       <c r="L10" t="n">
-        <v>36.65652856413775</v>
+        <v>36.65651799240443</v>
       </c>
       <c r="M10" t="n">
-        <v>26.00846044031225</v>
+        <v>26.00845761595078</v>
       </c>
       <c r="N10" t="n">
-        <v>76.96539454584519</v>
+        <v>76.96539647445981</v>
       </c>
       <c r="O10" t="n">
         <v>64.23860782658853</v>
       </c>
       <c r="P10" t="n">
-        <v>19.04735375502822</v>
+        <v>19.04734934660532</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.81121657533509</v>
+        <v>16.81123105226668</v>
       </c>
       <c r="R10" t="n">
-        <v>15.4421766453774</v>
+        <v>15.4421963386063</v>
       </c>
       <c r="S10" t="n">
-        <v>17.84355705706989</v>
+        <v>17.84357433742739</v>
       </c>
     </row>
     <row r="11">
@@ -1084,55 +1084,55 @@
         <v>100</v>
       </c>
       <c r="C11" t="n">
-        <v>8.136644390503294</v>
+        <v>16.62541028372744</v>
       </c>
       <c r="D11" t="n">
-        <v>16.62540233812668</v>
+        <v>8.136649687570468</v>
       </c>
       <c r="E11" t="n">
-        <v>23.06169387706454</v>
+        <v>23.061641134621</v>
       </c>
       <c r="F11" t="n">
-        <v>15.06127465780693</v>
+        <v>15.06127328786417</v>
       </c>
       <c r="G11" t="n">
-        <v>11.58788960223959</v>
+        <v>11.5878964919124</v>
       </c>
       <c r="H11" t="n">
-        <v>83.54489503625108</v>
+        <v>83.54488927351068</v>
       </c>
       <c r="I11" t="n">
-        <v>71.21134707790709</v>
+        <v>71.21136065236553</v>
       </c>
       <c r="J11" t="n">
-        <v>69.14933152056128</v>
+        <v>69.14932398977041</v>
       </c>
       <c r="K11" t="n">
-        <v>64.34640953497029</v>
+        <v>64.34641100338536</v>
       </c>
       <c r="L11" t="n">
         <v>42.99566939086458</v>
       </c>
       <c r="M11" t="n">
-        <v>33.16334035716022</v>
+        <v>33.16334528195168</v>
       </c>
       <c r="N11" t="n">
-        <v>75.53231754530312</v>
+        <v>75.53232290068988</v>
       </c>
       <c r="O11" t="n">
-        <v>63.92562440462393</v>
+        <v>63.92562109037927</v>
       </c>
       <c r="P11" t="n">
-        <v>17.26398621709959</v>
+        <v>17.2640002012144</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.9835942055925</v>
+        <v>13.98359990746814</v>
       </c>
       <c r="R11" t="n">
-        <v>10.17382999573393</v>
+        <v>10.17383949881744</v>
       </c>
       <c r="S11" t="n">
-        <v>15.36652590292581</v>
+        <v>15.36653629145119</v>
       </c>
     </row>
     <row r="12">
@@ -1145,55 +1145,55 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>9.191607292268463</v>
+        <v>15.62945372507764</v>
       </c>
       <c r="D12" t="n">
-        <v>15.62944829262727</v>
+        <v>9.19159380563006</v>
       </c>
       <c r="E12" t="n">
-        <v>32.18715530436268</v>
+        <v>32.18716765528992</v>
       </c>
       <c r="F12" t="n">
-        <v>13.72606645433656</v>
+        <v>13.7260670995021</v>
       </c>
       <c r="G12" t="n">
-        <v>9.831506336482084</v>
+        <v>9.831504126593094</v>
       </c>
       <c r="H12" t="n">
-        <v>73.6300895461371</v>
+        <v>73.63008833067489</v>
       </c>
       <c r="I12" t="n">
-        <v>71.37489199087518</v>
+        <v>71.37488134673058</v>
       </c>
       <c r="J12" t="n">
-        <v>57.42502889515384</v>
+        <v>57.42500746394778</v>
       </c>
       <c r="K12" t="n">
-        <v>61.28002452300661</v>
+        <v>61.28003524461221</v>
       </c>
       <c r="L12" t="n">
-        <v>43.11223520850158</v>
+        <v>43.11222568673876</v>
       </c>
       <c r="M12" t="n">
-        <v>31.46759232610445</v>
+        <v>31.46759366920821</v>
       </c>
       <c r="N12" t="n">
-        <v>69.78259685042943</v>
+        <v>69.7825898676967</v>
       </c>
       <c r="O12" t="n">
-        <v>57.10256961659452</v>
+        <v>57.10254777439692</v>
       </c>
       <c r="P12" t="n">
-        <v>28.18176808298973</v>
+        <v>28.18179311956822</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.27177164267659</v>
+        <v>21.27177112470426</v>
       </c>
       <c r="R12" t="n">
-        <v>16.57634828422101</v>
+        <v>16.57637132735022</v>
       </c>
       <c r="S12" t="n">
-        <v>18.17075862197133</v>
+        <v>18.17078173415507</v>
       </c>
     </row>
     <row r="13">
@@ -1206,55 +1206,55 @@
         <v>111</v>
       </c>
       <c r="C13" t="n">
-        <v>7.769431085995981</v>
+        <v>11.17503985378358</v>
       </c>
       <c r="D13" t="n">
-        <v>11.17505064487812</v>
+        <v>7.769428331951045</v>
       </c>
       <c r="E13" t="n">
-        <v>20.0899641904565</v>
+        <v>20.08998327769045</v>
       </c>
       <c r="F13" t="n">
-        <v>14.59918113559427</v>
+        <v>14.59917954647301</v>
       </c>
       <c r="G13" t="n">
-        <v>11.72226442875253</v>
+        <v>11.72226920435323</v>
       </c>
       <c r="H13" t="n">
-        <v>86.83165915213864</v>
+        <v>86.83166833359878</v>
       </c>
       <c r="I13" t="n">
-        <v>81.91170891368003</v>
+        <v>81.91170831398244</v>
       </c>
       <c r="J13" t="n">
-        <v>77.31958437614296</v>
+        <v>77.31959952445696</v>
       </c>
       <c r="K13" t="n">
-        <v>75.65633553895852</v>
+        <v>75.65634926933998</v>
       </c>
       <c r="L13" t="n">
-        <v>38.04005633085304</v>
+        <v>38.04005106313985</v>
       </c>
       <c r="M13" t="n">
-        <v>30.07473546493593</v>
+        <v>30.07473984182345</v>
       </c>
       <c r="N13" t="n">
-        <v>82.58154718384188</v>
+        <v>82.5815311514108</v>
       </c>
       <c r="O13" t="n">
-        <v>75.02523518636522</v>
+        <v>75.02523911347504</v>
       </c>
       <c r="P13" t="n">
-        <v>11.74781381403011</v>
+        <v>11.7478458492678</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.48276222458406</v>
+        <v>10.48279493475617</v>
       </c>
       <c r="R13" t="n">
-        <v>9.141777267278945</v>
+        <v>9.141810895082461</v>
       </c>
       <c r="S13" t="n">
-        <v>10.8392035261567</v>
+        <v>10.83922773513111</v>
       </c>
     </row>
     <row r="14">
@@ -1267,55 +1267,55 @@
         <v>135</v>
       </c>
       <c r="C14" t="n">
-        <v>11.43234842874187</v>
+        <v>18.04277315685715</v>
       </c>
       <c r="D14" t="n">
-        <v>18.04277042223873</v>
+        <v>11.43234555511641</v>
       </c>
       <c r="E14" t="n">
-        <v>35.08002754169089</v>
+        <v>35.08001712080542</v>
       </c>
       <c r="F14" t="n">
-        <v>13.56279243713692</v>
+        <v>13.56278942673219</v>
       </c>
       <c r="G14" t="n">
-        <v>9.872108889087171</v>
+        <v>9.872108136490903</v>
       </c>
       <c r="H14" t="n">
-        <v>79.66308574515126</v>
+        <v>79.66308207213544</v>
       </c>
       <c r="I14" t="n">
-        <v>72.82897249958401</v>
+        <v>72.8289844650065</v>
       </c>
       <c r="J14" t="n">
-        <v>64.69731186872812</v>
+        <v>64.6973109459579</v>
       </c>
       <c r="K14" t="n">
-        <v>62.41748143617773</v>
+        <v>62.41749439891896</v>
       </c>
       <c r="L14" t="n">
-        <v>41.23009268532424</v>
+        <v>41.23008446835537</v>
       </c>
       <c r="M14" t="n">
-        <v>30.46570778308878</v>
+        <v>30.4657091407841</v>
       </c>
       <c r="N14" t="n">
-        <v>73.57284055081534</v>
+        <v>73.57284124602566</v>
       </c>
       <c r="O14" t="n">
-        <v>61.43472373762543</v>
+        <v>61.43472576791427</v>
       </c>
       <c r="P14" t="n">
-        <v>21.67259636385544</v>
+        <v>21.67258743338195</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.70469219383332</v>
+        <v>20.70469421262085</v>
       </c>
       <c r="R14" t="n">
-        <v>19.6068153529354</v>
+        <v>19.60682992496999</v>
       </c>
       <c r="S14" t="n">
-        <v>21.75591109656921</v>
+        <v>21.75590806373265</v>
       </c>
     </row>
     <row r="15">
@@ -1328,55 +1328,55 @@
         <v>990</v>
       </c>
       <c r="C15" t="n">
-        <v>10.49614108208635</v>
+        <v>17.23498750082465</v>
       </c>
       <c r="D15" t="n">
-        <v>17.23499245327849</v>
+        <v>10.49613846631543</v>
       </c>
       <c r="E15" t="n">
-        <v>31.73961191297962</v>
+        <v>31.7396139140854</v>
       </c>
       <c r="F15" t="n">
-        <v>14.25203918417908</v>
+        <v>14.25203966606069</v>
       </c>
       <c r="G15" t="n">
-        <v>10.77539670075436</v>
+        <v>10.77539804799566</v>
       </c>
       <c r="H15" t="n">
-        <v>75.20639013310408</v>
+        <v>75.20639475609967</v>
       </c>
       <c r="I15" t="n">
-        <v>66.14817068120774</v>
+        <v>66.14817387781058</v>
       </c>
       <c r="J15" t="n">
         <v>56.63438180487329</v>
       </c>
       <c r="K15" t="n">
-        <v>58.45034749985323</v>
+        <v>58.45035664534002</v>
       </c>
       <c r="L15" t="n">
-        <v>43.3267271617224</v>
+        <v>43.32672623972515</v>
       </c>
       <c r="M15" t="n">
-        <v>38.19007881353032</v>
+        <v>38.19008372886042</v>
       </c>
       <c r="N15" t="n">
-        <v>67.42766108226533</v>
+        <v>67.42766537651038</v>
       </c>
       <c r="O15" t="n">
-        <v>54.96320369182031</v>
+        <v>54.96321152534005</v>
       </c>
       <c r="P15" t="n">
-        <v>25.17664797959365</v>
+        <v>25.1766662755037</v>
       </c>
       <c r="Q15" t="n">
-        <v>20.08490401971424</v>
+        <v>20.08490075997572</v>
       </c>
       <c r="R15" t="n">
-        <v>14.5627817713201</v>
+        <v>14.56275206280172</v>
       </c>
       <c r="S15" t="n">
-        <v>20.49777545164364</v>
+        <v>20.49777428265139</v>
       </c>
     </row>
     <row r="16">
@@ -1389,55 +1389,55 @@
         <v>920</v>
       </c>
       <c r="C16" t="n">
-        <v>11.50472116009058</v>
+        <v>20.0907790896819</v>
       </c>
       <c r="D16" t="n">
-        <v>20.0907813971406</v>
+        <v>11.50472089498326</v>
       </c>
       <c r="E16" t="n">
-        <v>35.95209650692843</v>
+        <v>35.95206844540916</v>
       </c>
       <c r="F16" t="n">
-        <v>8.643516155998586</v>
+        <v>8.643517065623231</v>
       </c>
       <c r="G16" t="n">
-        <v>6.28946241447637</v>
+        <v>6.289460296847528</v>
       </c>
       <c r="H16" t="n">
-        <v>70.03722036596409</v>
+        <v>70.03722190311515</v>
       </c>
       <c r="I16" t="n">
-        <v>67.05843982457118</v>
+        <v>67.05844177129207</v>
       </c>
       <c r="J16" t="n">
-        <v>51.21683299614371</v>
+        <v>51.21684034494471</v>
       </c>
       <c r="K16" t="n">
-        <v>50.87443391070807</v>
+        <v>50.87445505347964</v>
       </c>
       <c r="L16" t="n">
-        <v>28.97824245365395</v>
+        <v>28.97824781293718</v>
       </c>
       <c r="M16" t="n">
-        <v>19.08673100066436</v>
+        <v>19.08672843478694</v>
       </c>
       <c r="N16" t="n">
-        <v>67.32351098398796</v>
+        <v>67.32350936491376</v>
       </c>
       <c r="O16" t="n">
-        <v>49.64208986955087</v>
+        <v>49.64209385971022</v>
       </c>
       <c r="P16" t="n">
-        <v>27.31317727737172</v>
+        <v>27.31319990839199</v>
       </c>
       <c r="Q16" t="n">
-        <v>26.99846668556689</v>
+        <v>26.9984928764924</v>
       </c>
       <c r="R16" t="n">
-        <v>26.67647583425556</v>
+        <v>26.67650553376603</v>
       </c>
       <c r="S16" t="n">
-        <v>28.11801474291721</v>
+        <v>28.11800975568083</v>
       </c>
     </row>
   </sheetData>

--- a/2d/results/best_unet_nofilter_projection_max/best_unet.xlsx
+++ b/2d/results/best_unet_nofilter_projection_max/best_unet.xlsx
@@ -535,55 +535,55 @@
         <v>140</v>
       </c>
       <c r="C2" t="n">
-        <v>20.49904283311987</v>
+        <v>25.80084376621848</v>
       </c>
       <c r="D2" t="n">
-        <v>12.52457605167334</v>
+        <v>10.81457776328362</v>
       </c>
       <c r="E2" t="n">
-        <v>39.1369232159589</v>
+        <v>34.38209586870084</v>
       </c>
       <c r="F2" t="n">
-        <v>13.21549753058586</v>
+        <v>15.22052631476081</v>
       </c>
       <c r="G2" t="n">
-        <v>10.62963219284083</v>
+        <v>12.63590316478953</v>
       </c>
       <c r="H2" t="n">
-        <v>77.87706031237225</v>
+        <v>84.08162621405295</v>
       </c>
       <c r="I2" t="n">
-        <v>74.03852880714756</v>
+        <v>73.84476763982924</v>
       </c>
       <c r="J2" t="n">
-        <v>65.49213725717293</v>
+        <v>70.07796887142082</v>
       </c>
       <c r="K2" t="n">
-        <v>63.97596420931025</v>
+        <v>66.83418712759351</v>
       </c>
       <c r="L2" t="n">
-        <v>38.2812065058835</v>
+        <v>42.45209247100843</v>
       </c>
       <c r="M2" t="n">
-        <v>31.387654515447</v>
+        <v>36.80931550906026</v>
       </c>
       <c r="N2" t="n">
-        <v>73.70863277078395</v>
+        <v>76.62088548438575</v>
       </c>
       <c r="O2" t="n">
-        <v>62.27466674803021</v>
+        <v>66.06400479562831</v>
       </c>
       <c r="P2" t="n">
-        <v>21.85434598001351</v>
+        <v>22.74615241704739</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.51553412451567</v>
+        <v>18.51048481912611</v>
       </c>
       <c r="R2" t="n">
-        <v>21.16816364248647</v>
+        <v>15.12819250453505</v>
       </c>
       <c r="S2" t="n">
-        <v>22.40760878049781</v>
+        <v>20.217926603163</v>
       </c>
     </row>
     <row r="3">
@@ -596,55 +596,55 @@
         <v>141</v>
       </c>
       <c r="C3" t="n">
-        <v>13.99224099699725</v>
+        <v>20.49544282081968</v>
       </c>
       <c r="D3" t="n">
-        <v>8.794688210870428</v>
+        <v>7.947988398908396</v>
       </c>
       <c r="E3" t="n">
-        <v>30.12154322452308</v>
+        <v>36.78118091712028</v>
       </c>
       <c r="F3" t="n">
-        <v>21.57314533112797</v>
+        <v>25.70942450009868</v>
       </c>
       <c r="G3" t="n">
-        <v>16.28924917968719</v>
+        <v>19.68398066977178</v>
       </c>
       <c r="H3" t="n">
-        <v>81.9200745561927</v>
+        <v>96.74119478682299</v>
       </c>
       <c r="I3" t="n">
-        <v>88.85118004293436</v>
+        <v>91.66061653017462</v>
       </c>
       <c r="J3" t="n">
-        <v>71.96860652063891</v>
+        <v>79.83354921300038</v>
       </c>
       <c r="K3" t="n">
-        <v>78.61143581267639</v>
+        <v>81.95940426978176</v>
       </c>
       <c r="L3" t="n">
-        <v>55.34586166600285</v>
+        <v>61.52703153317722</v>
       </c>
       <c r="M3" t="n">
-        <v>44.86435553846503</v>
+        <v>50.67600924640708</v>
       </c>
       <c r="N3" t="n">
-        <v>80.97743688818984</v>
+        <v>88.79418518777248</v>
       </c>
       <c r="O3" t="n">
-        <v>71.71699148228927</v>
+        <v>77.72666255085811</v>
       </c>
       <c r="P3" t="n">
-        <v>14.86719082399782</v>
+        <v>19.29658288669654</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.31678480665137</v>
+        <v>17.49803930059348</v>
       </c>
       <c r="R3" t="n">
-        <v>15.40497692320785</v>
+        <v>15.64745789497297</v>
       </c>
       <c r="S3" t="n">
-        <v>14.34458512670731</v>
+        <v>15.97348706593524</v>
       </c>
     </row>
     <row r="4">
@@ -657,55 +657,55 @@
         <v>149</v>
       </c>
       <c r="C4" t="n">
-        <v>9.747684072554899</v>
+        <v>12.03354756685249</v>
       </c>
       <c r="D4" t="n">
-        <v>8.992947897165898</v>
+        <v>13.48474684523039</v>
       </c>
       <c r="E4" t="n">
-        <v>17.31701246194098</v>
+        <v>21.73435275755527</v>
       </c>
       <c r="F4" t="n">
-        <v>11.22912751715172</v>
+        <v>13.8318939579944</v>
       </c>
       <c r="G4" t="n">
-        <v>9.326822388156794</v>
+        <v>10.95564240753127</v>
       </c>
       <c r="H4" t="n">
-        <v>83.69719260942017</v>
+        <v>88.37455539351502</v>
       </c>
       <c r="I4" t="n">
-        <v>74.63556526714429</v>
+        <v>75.11656004376468</v>
       </c>
       <c r="J4" t="n">
-        <v>71.66145464944898</v>
+        <v>77.71567996728734</v>
       </c>
       <c r="K4" t="n">
-        <v>64.94637488154302</v>
+        <v>60.83006560358393</v>
       </c>
       <c r="L4" t="n">
-        <v>33.62717534537394</v>
+        <v>39.89593025176224</v>
       </c>
       <c r="M4" t="n">
-        <v>27.22986394378596</v>
+        <v>33.66567096968661</v>
       </c>
       <c r="N4" t="n">
-        <v>77.49978766405916</v>
+        <v>80.05826698315531</v>
       </c>
       <c r="O4" t="n">
-        <v>66.85769590960682</v>
+        <v>67.11181876698294</v>
       </c>
       <c r="P4" t="n">
-        <v>15.20904248013925</v>
+        <v>14.25393671386435</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.95763638770714</v>
+        <v>17.16925857812009</v>
       </c>
       <c r="R4" t="n">
-        <v>18.92709261040561</v>
+        <v>20.62323144531993</v>
       </c>
       <c r="S4" t="n">
-        <v>17.2767030058125</v>
+        <v>18.12239025770451</v>
       </c>
     </row>
     <row r="5">
@@ -718,55 +718,55 @@
         <v>160</v>
       </c>
       <c r="C5" t="n">
-        <v>18.2538172869583</v>
+        <v>19.31757052884388</v>
       </c>
       <c r="D5" t="n">
-        <v>12.55164052255571</v>
+        <v>11.78865842836309</v>
       </c>
       <c r="E5" t="n">
-        <v>41.62515501020552</v>
+        <v>27.94209046456333</v>
       </c>
       <c r="F5" t="n">
-        <v>11.3522140070596</v>
+        <v>14.31602987405276</v>
       </c>
       <c r="G5" t="n">
-        <v>8.307198746283692</v>
+        <v>12.00202575183357</v>
       </c>
       <c r="H5" t="n">
-        <v>69.13085646270271</v>
+        <v>80.38330086703009</v>
       </c>
       <c r="I5" t="n">
-        <v>67.95497720904854</v>
+        <v>71.33022238567018</v>
       </c>
       <c r="J5" t="n">
-        <v>55.21008124573568</v>
+        <v>65.18282266092226</v>
       </c>
       <c r="K5" t="n">
-        <v>53.53137626865396</v>
+        <v>60.13597286769613</v>
       </c>
       <c r="L5" t="n">
-        <v>35.79698719995523</v>
+        <v>43.2561371090928</v>
       </c>
       <c r="M5" t="n">
-        <v>30.0759247699961</v>
+        <v>35.2228645832312</v>
       </c>
       <c r="N5" t="n">
-        <v>66.46433618190615</v>
+        <v>73.084010170139</v>
       </c>
       <c r="O5" t="n">
-        <v>51.69721577053483</v>
+        <v>59.12929320730984</v>
       </c>
       <c r="P5" t="n">
-        <v>26.04479473885856</v>
+        <v>20.66306994744168</v>
       </c>
       <c r="Q5" t="n">
-        <v>25.09503587734168</v>
+        <v>21.69393492870601</v>
       </c>
       <c r="R5" t="n">
-        <v>24.89938413957432</v>
+        <v>24.45609409259677</v>
       </c>
       <c r="S5" t="n">
-        <v>26.13955123026939</v>
+        <v>22.70215598128026</v>
       </c>
     </row>
     <row r="6">
@@ -779,55 +779,55 @@
         <v>170</v>
       </c>
       <c r="C6" t="n">
-        <v>15.56077127328608</v>
+        <v>16.76705155569219</v>
       </c>
       <c r="D6" t="n">
-        <v>9.361367779630703</v>
+        <v>13.84212773355678</v>
       </c>
       <c r="E6" t="n">
-        <v>24.95314342826614</v>
+        <v>22.54150391789825</v>
       </c>
       <c r="F6" t="n">
-        <v>15.29998389802067</v>
+        <v>17.81875569187643</v>
       </c>
       <c r="G6" t="n">
-        <v>11.48215697144594</v>
+        <v>13.98571976247371</v>
       </c>
       <c r="H6" t="n">
-        <v>80.51633563309825</v>
+        <v>92.25308465689737</v>
       </c>
       <c r="I6" t="n">
-        <v>75.59966507624627</v>
+        <v>80.64871741780794</v>
       </c>
       <c r="J6" t="n">
-        <v>57.79641390005387</v>
+        <v>61.74495565276233</v>
       </c>
       <c r="K6" t="n">
-        <v>62.26919126831923</v>
+        <v>60.50793930064766</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75994258344779</v>
+        <v>53.78058758738162</v>
       </c>
       <c r="M6" t="n">
-        <v>37.9969693086047</v>
+        <v>44.97268259771235</v>
       </c>
       <c r="N6" t="n">
-        <v>74.95035297349176</v>
+        <v>82.02409946741393</v>
       </c>
       <c r="O6" t="n">
-        <v>56.62663987584099</v>
+        <v>55.75014112362132</v>
       </c>
       <c r="P6" t="n">
-        <v>29.28536532905791</v>
+        <v>33.07003675551794</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.2415670485119</v>
+        <v>28.49077821606646</v>
       </c>
       <c r="R6" t="n">
-        <v>18.92805975002668</v>
+        <v>24.9734636359053</v>
       </c>
       <c r="S6" t="n">
-        <v>26.56136801113639</v>
+        <v>32.08454099391754</v>
       </c>
     </row>
     <row r="7">
@@ -840,55 +840,55 @@
         <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>13.41706728782088</v>
+        <v>12.69361261536545</v>
       </c>
       <c r="D7" t="n">
-        <v>10.68150665678733</v>
+        <v>13.29474100902478</v>
       </c>
       <c r="E7" t="n">
-        <v>26.97616734959997</v>
+        <v>43.11469418845146</v>
       </c>
       <c r="F7" t="n">
-        <v>12.71268822455215</v>
+        <v>15.19823332688466</v>
       </c>
       <c r="G7" t="n">
-        <v>9.58601204667168</v>
+        <v>11.63454417949527</v>
       </c>
       <c r="H7" t="n">
-        <v>80.60984066773732</v>
+        <v>87.53362899846915</v>
       </c>
       <c r="I7" t="n">
-        <v>74.33394301207791</v>
+        <v>74.06431481410664</v>
       </c>
       <c r="J7" t="n">
-        <v>65.86130614331073</v>
+        <v>71.30080850118318</v>
       </c>
       <c r="K7" t="n">
-        <v>64.17769329334402</v>
+        <v>66.67916161492393</v>
       </c>
       <c r="L7" t="n">
-        <v>35.66327140190991</v>
+        <v>43.07529836315521</v>
       </c>
       <c r="M7" t="n">
-        <v>28.58039293499436</v>
+        <v>32.99354630668947</v>
       </c>
       <c r="N7" t="n">
-        <v>74.63399332718927</v>
+        <v>76.77151997277896</v>
       </c>
       <c r="O7" t="n">
-        <v>63.79415123125349</v>
+        <v>68.165129303513</v>
       </c>
       <c r="P7" t="n">
-        <v>20.10368087334519</v>
+        <v>18.54466755579146</v>
       </c>
       <c r="Q7" t="n">
-        <v>19.35179946156579</v>
+        <v>19.24926104256229</v>
       </c>
       <c r="R7" t="n">
-        <v>18.52827823965129</v>
+        <v>20.0832849646166</v>
       </c>
       <c r="S7" t="n">
-        <v>18.86491407429363</v>
+        <v>16.33350638268175</v>
       </c>
     </row>
     <row r="8">
@@ -901,55 +901,55 @@
         <v>190</v>
       </c>
       <c r="C8" t="n">
-        <v>11.67889609397331</v>
+        <v>13.78933670252688</v>
       </c>
       <c r="D8" t="n">
-        <v>4.896858663447884</v>
+        <v>6.550151506299465</v>
       </c>
       <c r="E8" t="n">
-        <v>34.58458452998283</v>
+        <v>23.34353659800245</v>
       </c>
       <c r="F8" t="n">
-        <v>17.396728366405</v>
+        <v>20.33049301141859</v>
       </c>
       <c r="G8" t="n">
-        <v>11.41095454144132</v>
+        <v>15.58463693474376</v>
       </c>
       <c r="H8" t="n">
-        <v>97.87542353418677</v>
+        <v>101.2288549883569</v>
       </c>
       <c r="I8" t="n">
-        <v>88.68199976975174</v>
+        <v>86.26664551836279</v>
       </c>
       <c r="J8" t="n">
-        <v>68.84939453821424</v>
+        <v>82.54679371907061</v>
       </c>
       <c r="K8" t="n">
-        <v>71.00940350618367</v>
+        <v>76.18624313409998</v>
       </c>
       <c r="L8" t="n">
-        <v>40.93781122284466</v>
+        <v>47.69839198132696</v>
       </c>
       <c r="M8" t="n">
-        <v>33.07906915159433</v>
+        <v>40.49545423319042</v>
       </c>
       <c r="N8" t="n">
-        <v>91.31837283925955</v>
+        <v>91.31704315206782</v>
       </c>
       <c r="O8" t="n">
-        <v>68.41639334002926</v>
+        <v>76.748923584789</v>
       </c>
       <c r="P8" t="n">
-        <v>29.65609541994376</v>
+        <v>18.57146888721827</v>
       </c>
       <c r="Q8" t="n">
-        <v>25.03177007513627</v>
+        <v>15.34367170017317</v>
       </c>
       <c r="R8" t="n">
-        <v>19.92805339240439</v>
+        <v>11.69239017056047</v>
       </c>
       <c r="S8" t="n">
-        <v>25.07926804559123</v>
+        <v>15.95334130893719</v>
       </c>
     </row>
     <row r="9">
@@ -962,55 +962,55 @@
         <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>23.45414375702097</v>
+        <v>23.83074727128066</v>
       </c>
       <c r="D9" t="n">
-        <v>14.91290377942081</v>
+        <v>14.14148891572596</v>
       </c>
       <c r="E9" t="n">
-        <v>21.18649475719666</v>
+        <v>18.53093882441832</v>
       </c>
       <c r="F9" t="n">
-        <v>14.65915202702977</v>
+        <v>16.97117897044867</v>
       </c>
       <c r="G9" t="n">
-        <v>11.80485360232924</v>
+        <v>14.39956366435463</v>
       </c>
       <c r="H9" t="n">
-        <v>83.98920640682978</v>
+        <v>93.0506872356593</v>
       </c>
       <c r="I9" t="n">
-        <v>77.03537330142511</v>
+        <v>80.14966119337826</v>
       </c>
       <c r="J9" t="n">
-        <v>70.90262682456903</v>
+        <v>76.50612579276955</v>
       </c>
       <c r="K9" t="n">
-        <v>65.94594096369964</v>
+        <v>68.23515791494627</v>
       </c>
       <c r="L9" t="n">
-        <v>40.73066951357511</v>
+        <v>45.69424913949609</v>
       </c>
       <c r="M9" t="n">
-        <v>35.53665065362953</v>
+        <v>38.74055683861106</v>
       </c>
       <c r="N9" t="n">
-        <v>78.60409901112003</v>
+        <v>84.06234725299578</v>
       </c>
       <c r="O9" t="n">
-        <v>66.27242374925174</v>
+        <v>69.24815222055066</v>
       </c>
       <c r="P9" t="n">
-        <v>17.556888274912</v>
+        <v>25.18270532051172</v>
       </c>
       <c r="Q9" t="n">
-        <v>17.14185925656118</v>
+        <v>21.31711603228977</v>
       </c>
       <c r="R9" t="n">
-        <v>16.68936637707971</v>
+        <v>16.82931490519565</v>
       </c>
       <c r="S9" t="n">
-        <v>18.30823360989051</v>
+        <v>21.6989291998145</v>
       </c>
     </row>
     <row r="10">
@@ -1023,55 +1023,55 @@
         <v>199</v>
       </c>
       <c r="C10" t="n">
-        <v>14.29815362977604</v>
+        <v>17.4487366723356</v>
       </c>
       <c r="D10" t="n">
-        <v>9.60849285555436</v>
+        <v>10.86625084663734</v>
       </c>
       <c r="E10" t="n">
-        <v>36.42042255407032</v>
+        <v>29.6744374020187</v>
       </c>
       <c r="F10" t="n">
-        <v>13.38671015281071</v>
+        <v>15.7268840585521</v>
       </c>
       <c r="G10" t="n">
-        <v>8.511213749068414</v>
+        <v>11.07289848394364</v>
       </c>
       <c r="H10" t="n">
-        <v>79.69720583881453</v>
+        <v>91.81113532234329</v>
       </c>
       <c r="I10" t="n">
-        <v>76.92824594941679</v>
+        <v>82.45955920935958</v>
       </c>
       <c r="J10" t="n">
-        <v>64.51700062321238</v>
+        <v>76.71203644119271</v>
       </c>
       <c r="K10" t="n">
-        <v>66.92563629670538</v>
+        <v>71.02710251014645</v>
       </c>
       <c r="L10" t="n">
-        <v>36.65651799240443</v>
+        <v>40.68080848666025</v>
       </c>
       <c r="M10" t="n">
-        <v>26.00845761595078</v>
+        <v>29.16681567920101</v>
       </c>
       <c r="N10" t="n">
-        <v>76.96539647445981</v>
+        <v>85.90645272500481</v>
       </c>
       <c r="O10" t="n">
-        <v>64.23860782658853</v>
+        <v>72.7319888434277</v>
       </c>
       <c r="P10" t="n">
-        <v>19.04734934660532</v>
+        <v>16.44582525653187</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.81123105226668</v>
+        <v>15.25724298596576</v>
       </c>
       <c r="R10" t="n">
-        <v>15.4421963386063</v>
+        <v>14.26736702148982</v>
       </c>
       <c r="S10" t="n">
-        <v>17.84357433742739</v>
+        <v>15.33582573098426</v>
       </c>
     </row>
     <row r="11">
@@ -1084,55 +1084,55 @@
         <v>100</v>
       </c>
       <c r="C11" t="n">
-        <v>16.62541028372744</v>
+        <v>17.24816189419774</v>
       </c>
       <c r="D11" t="n">
-        <v>8.136649687570468</v>
+        <v>11.46331089316126</v>
       </c>
       <c r="E11" t="n">
-        <v>23.061641134621</v>
+        <v>19.02935485666584</v>
       </c>
       <c r="F11" t="n">
-        <v>15.06127328786417</v>
+        <v>19.51548951439109</v>
       </c>
       <c r="G11" t="n">
-        <v>11.5878964919124</v>
+        <v>15.83421201877195</v>
       </c>
       <c r="H11" t="n">
-        <v>83.54488927351068</v>
+        <v>103.2049392039557</v>
       </c>
       <c r="I11" t="n">
-        <v>71.21136065236553</v>
+        <v>82.50853103783201</v>
       </c>
       <c r="J11" t="n">
-        <v>69.14932398977041</v>
+        <v>87.48433894998892</v>
       </c>
       <c r="K11" t="n">
-        <v>64.34641100338536</v>
+        <v>71.14161866292166</v>
       </c>
       <c r="L11" t="n">
-        <v>42.99566939086458</v>
+        <v>52.56089017087</v>
       </c>
       <c r="M11" t="n">
-        <v>33.16334528195168</v>
+        <v>40.7664345813486</v>
       </c>
       <c r="N11" t="n">
-        <v>75.53232290068988</v>
+        <v>90.73933802853918</v>
       </c>
       <c r="O11" t="n">
-        <v>63.92562109037927</v>
+        <v>76.50605219252239</v>
       </c>
       <c r="P11" t="n">
-        <v>17.2640002012144</v>
+        <v>15.23241075012836</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.98359990746814</v>
+        <v>14.95702106381861</v>
       </c>
       <c r="R11" t="n">
-        <v>10.17383949881744</v>
+        <v>15.82853763252487</v>
       </c>
       <c r="S11" t="n">
-        <v>15.36653629145119</v>
+        <v>17.00406532281561</v>
       </c>
     </row>
     <row r="12">
@@ -1145,55 +1145,55 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62945372507764</v>
+        <v>24.48357144002748</v>
       </c>
       <c r="D12" t="n">
-        <v>9.19159380563006</v>
+        <v>17.77056886061054</v>
       </c>
       <c r="E12" t="n">
-        <v>32.18716765528992</v>
+        <v>38.56410550429469</v>
       </c>
       <c r="F12" t="n">
-        <v>13.7260670995021</v>
+        <v>14.58809884165764</v>
       </c>
       <c r="G12" t="n">
-        <v>9.831504126593094</v>
+        <v>9.422868556269821</v>
       </c>
       <c r="H12" t="n">
-        <v>73.63008833067489</v>
+        <v>79.12140077381908</v>
       </c>
       <c r="I12" t="n">
-        <v>71.37488134673058</v>
+        <v>73.95107891132504</v>
       </c>
       <c r="J12" t="n">
-        <v>57.42500746394778</v>
+        <v>53.12370397060801</v>
       </c>
       <c r="K12" t="n">
-        <v>61.28003524461221</v>
+        <v>60.16603460561629</v>
       </c>
       <c r="L12" t="n">
-        <v>43.11222568673876</v>
+        <v>43.38358372618406</v>
       </c>
       <c r="M12" t="n">
-        <v>31.46759366920821</v>
+        <v>33.79741318974789</v>
       </c>
       <c r="N12" t="n">
-        <v>69.7825898676967</v>
+        <v>71.54124812286329</v>
       </c>
       <c r="O12" t="n">
-        <v>57.10254777439692</v>
+        <v>55.17556910573774</v>
       </c>
       <c r="P12" t="n">
-        <v>28.18179311956822</v>
+        <v>34.44251074991001</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.27177112470426</v>
+        <v>29.38506111419564</v>
       </c>
       <c r="R12" t="n">
-        <v>16.57637132735022</v>
+        <v>23.9740176864103</v>
       </c>
       <c r="S12" t="n">
-        <v>18.17078173415507</v>
+        <v>24.81878651880694</v>
       </c>
     </row>
     <row r="13">
@@ -1206,55 +1206,55 @@
         <v>111</v>
       </c>
       <c r="C13" t="n">
-        <v>11.17503985378358</v>
+        <v>10.11998252334652</v>
       </c>
       <c r="D13" t="n">
-        <v>7.769428331951045</v>
+        <v>7.62134837798345</v>
       </c>
       <c r="E13" t="n">
-        <v>20.08998327769045</v>
+        <v>19.78348918417602</v>
       </c>
       <c r="F13" t="n">
-        <v>14.59917954647301</v>
+        <v>18.34034934246767</v>
       </c>
       <c r="G13" t="n">
-        <v>11.72226920435323</v>
+        <v>14.91591211580278</v>
       </c>
       <c r="H13" t="n">
-        <v>86.83166833359878</v>
+        <v>92.01801318743944</v>
       </c>
       <c r="I13" t="n">
-        <v>81.91170831398244</v>
+        <v>80.98038725935788</v>
       </c>
       <c r="J13" t="n">
-        <v>77.31959952445696</v>
+        <v>84.61221451408841</v>
       </c>
       <c r="K13" t="n">
-        <v>75.65634926933998</v>
+        <v>72.83460056432536</v>
       </c>
       <c r="L13" t="n">
-        <v>38.04005106313985</v>
+        <v>47.05524081770528</v>
       </c>
       <c r="M13" t="n">
-        <v>30.07473984182345</v>
+        <v>39.79020971232323</v>
       </c>
       <c r="N13" t="n">
-        <v>82.5815311514108</v>
+        <v>83.25872142288055</v>
       </c>
       <c r="O13" t="n">
-        <v>75.02523911347504</v>
+        <v>76.76217223696354</v>
       </c>
       <c r="P13" t="n">
-        <v>11.7478458492678</v>
+        <v>8.137086631237555</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.48279493475617</v>
+        <v>9.10503415989014</v>
       </c>
       <c r="R13" t="n">
-        <v>9.141810895082461</v>
+        <v>10.19923819842169</v>
       </c>
       <c r="S13" t="n">
-        <v>10.83922773513111</v>
+        <v>8.889237711312392</v>
       </c>
     </row>
     <row r="14">
@@ -1267,55 +1267,55 @@
         <v>135</v>
       </c>
       <c r="C14" t="n">
-        <v>18.04277315685715</v>
+        <v>21.35921015979393</v>
       </c>
       <c r="D14" t="n">
-        <v>11.43234555511641</v>
+        <v>12.46148363426569</v>
       </c>
       <c r="E14" t="n">
-        <v>35.08001712080542</v>
+        <v>36.7792400819089</v>
       </c>
       <c r="F14" t="n">
-        <v>13.56278942673219</v>
+        <v>18.40899249081005</v>
       </c>
       <c r="G14" t="n">
-        <v>9.872108136490903</v>
+        <v>13.08751776354665</v>
       </c>
       <c r="H14" t="n">
-        <v>79.66308207213544</v>
+        <v>88.23751762467457</v>
       </c>
       <c r="I14" t="n">
-        <v>72.8289844650065</v>
+        <v>79.03788695861097</v>
       </c>
       <c r="J14" t="n">
-        <v>64.6973109459579</v>
+        <v>72.45747841900972</v>
       </c>
       <c r="K14" t="n">
-        <v>62.41749439891896</v>
+        <v>65.31451216732728</v>
       </c>
       <c r="L14" t="n">
-        <v>41.23008446835537</v>
+        <v>56.86681303154021</v>
       </c>
       <c r="M14" t="n">
-        <v>30.4657091407841</v>
+        <v>37.17737179858489</v>
       </c>
       <c r="N14" t="n">
-        <v>73.57284124602566</v>
+        <v>78.31815306793754</v>
       </c>
       <c r="O14" t="n">
-        <v>61.43472576791427</v>
+        <v>65.9807032800215</v>
       </c>
       <c r="P14" t="n">
-        <v>21.67258743338195</v>
+        <v>26.46443099842838</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.70469421262085</v>
+        <v>22.96719571199436</v>
       </c>
       <c r="R14" t="n">
-        <v>19.60682992496999</v>
+        <v>24.99041672039771</v>
       </c>
       <c r="S14" t="n">
-        <v>21.75590806373265</v>
+        <v>21.85574288466879</v>
       </c>
     </row>
     <row r="15">
@@ -1328,55 +1328,55 @@
         <v>990</v>
       </c>
       <c r="C15" t="n">
-        <v>17.23498750082465</v>
+        <v>13.56220226539272</v>
       </c>
       <c r="D15" t="n">
-        <v>10.49613846631543</v>
+        <v>8.365616415205759</v>
       </c>
       <c r="E15" t="n">
-        <v>31.7396139140854</v>
+        <v>33.31492404254373</v>
       </c>
       <c r="F15" t="n">
-        <v>14.25203966606069</v>
+        <v>15.25806986297233</v>
       </c>
       <c r="G15" t="n">
-        <v>10.77539804799566</v>
+        <v>10.88105038212038</v>
       </c>
       <c r="H15" t="n">
-        <v>75.20639475609967</v>
+        <v>78.8282577141164</v>
       </c>
       <c r="I15" t="n">
-        <v>66.14817387781058</v>
+        <v>67.03092599757807</v>
       </c>
       <c r="J15" t="n">
-        <v>56.63438180487329</v>
+        <v>64.19076749711901</v>
       </c>
       <c r="K15" t="n">
-        <v>58.45035664534002</v>
+        <v>55.13503608421613</v>
       </c>
       <c r="L15" t="n">
-        <v>43.32672623972515</v>
+        <v>48.62874430236638</v>
       </c>
       <c r="M15" t="n">
-        <v>38.19008372886042</v>
+        <v>39.18866944548616</v>
       </c>
       <c r="N15" t="n">
-        <v>67.42766537651038</v>
+        <v>69.44225273963018</v>
       </c>
       <c r="O15" t="n">
-        <v>54.96321152534005</v>
+        <v>57.16749508036555</v>
       </c>
       <c r="P15" t="n">
-        <v>25.1766662755037</v>
+        <v>24.39727454256462</v>
       </c>
       <c r="Q15" t="n">
-        <v>20.08490075997572</v>
+        <v>23.19904385126654</v>
       </c>
       <c r="R15" t="n">
-        <v>14.56275206280172</v>
+        <v>21.76451923720219</v>
       </c>
       <c r="S15" t="n">
-        <v>20.49777428265139</v>
+        <v>21.0093079045668</v>
       </c>
     </row>
     <row r="16">
@@ -1389,55 +1389,55 @@
         <v>920</v>
       </c>
       <c r="C16" t="n">
-        <v>20.0907790896819</v>
+        <v>25.33978288248291</v>
       </c>
       <c r="D16" t="n">
-        <v>11.50472089498326</v>
+        <v>11.69588811731115</v>
       </c>
       <c r="E16" t="n">
-        <v>35.95206844540916</v>
+        <v>34.64170597627984</v>
       </c>
       <c r="F16" t="n">
-        <v>8.643517065623231</v>
+        <v>12.38925764930406</v>
       </c>
       <c r="G16" t="n">
-        <v>6.289460296847528</v>
+        <v>9.989603875286413</v>
       </c>
       <c r="H16" t="n">
-        <v>70.03722190311515</v>
+        <v>89.2333954262248</v>
       </c>
       <c r="I16" t="n">
-        <v>67.05844177129207</v>
+        <v>77.73752820275178</v>
       </c>
       <c r="J16" t="n">
-        <v>51.21684034494471</v>
+        <v>59.44777648994033</v>
       </c>
       <c r="K16" t="n">
-        <v>50.87445505347964</v>
+        <v>57.52770207333683</v>
       </c>
       <c r="L16" t="n">
-        <v>28.97824781293718</v>
+        <v>36.55322057478597</v>
       </c>
       <c r="M16" t="n">
-        <v>19.08672843478694</v>
+        <v>28.50508350337727</v>
       </c>
       <c r="N16" t="n">
-        <v>67.32350936491376</v>
+        <v>81.74584297732301</v>
       </c>
       <c r="O16" t="n">
-        <v>49.64209385971022</v>
+        <v>55.66571244968447</v>
       </c>
       <c r="P16" t="n">
-        <v>27.31319990839199</v>
+        <v>36.24783188235642</v>
       </c>
       <c r="Q16" t="n">
-        <v>26.9984928764924</v>
+        <v>36.15356648872147</v>
       </c>
       <c r="R16" t="n">
-        <v>26.67650553376603</v>
+        <v>36.05396596643573</v>
       </c>
       <c r="S16" t="n">
-        <v>28.11800975568083</v>
+        <v>37.88773002135137</v>
       </c>
     </row>
   </sheetData>
